--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2429"/>
+  <dimension ref="A1:F2430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48992,19 +48992,39 @@
         <v>46230</v>
       </c>
       <c r="B2429" t="n">
-        <v>180.79</v>
+        <v>180.7899932861328</v>
       </c>
       <c r="C2429" t="n">
-        <v>181.14</v>
+        <v>181.1399993896484</v>
       </c>
       <c r="D2429" t="n">
-        <v>179.65</v>
+        <v>179.6499938964844</v>
       </c>
       <c r="E2429" t="n">
-        <v>179.98</v>
+        <v>179.9799957275391</v>
       </c>
       <c r="F2429" t="n">
         <v>305427</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B2430" t="n">
+        <v>182.36</v>
+      </c>
+      <c r="C2430" t="n">
+        <v>184.27</v>
+      </c>
+      <c r="D2430" t="n">
+        <v>182.32</v>
+      </c>
+      <c r="E2430" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="F2430" t="n">
+        <v>5217</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -49012,19 +49012,19 @@
         <v>46231</v>
       </c>
       <c r="B2430" t="n">
-        <v>182.36</v>
+        <v>182.23</v>
       </c>
       <c r="C2430" t="n">
         <v>184.27</v>
       </c>
       <c r="D2430" t="n">
-        <v>182.32</v>
+        <v>182.08</v>
       </c>
       <c r="E2430" t="n">
         <v>183.8</v>
       </c>
       <c r="F2430" t="n">
-        <v>5217</v>
+        <v>258175</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -49012,19 +49012,19 @@
         <v>46231</v>
       </c>
       <c r="B2430" t="n">
-        <v>182.23</v>
+        <v>181.71</v>
       </c>
       <c r="C2430" t="n">
         <v>184.27</v>
       </c>
       <c r="D2430" t="n">
-        <v>182.08</v>
+        <v>181.71</v>
       </c>
       <c r="E2430" t="n">
         <v>183.8</v>
       </c>
       <c r="F2430" t="n">
-        <v>258175</v>
+        <v>1010481</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -49012,16 +49012,16 @@
         <v>46231</v>
       </c>
       <c r="B2430" t="n">
-        <v>181.71</v>
+        <v>181.7100067138672</v>
       </c>
       <c r="C2430" t="n">
-        <v>184.27</v>
+        <v>184.2700042724609</v>
       </c>
       <c r="D2430" t="n">
-        <v>181.71</v>
+        <v>181.7100067138672</v>
       </c>
       <c r="E2430" t="n">
-        <v>183.8</v>
+        <v>183.8000030517578</v>
       </c>
       <c r="F2430" t="n">
         <v>1010481</v>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2430"/>
+  <dimension ref="A1:F2431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49027,6 +49027,26 @@
         <v>1010481</v>
       </c>
     </row>
+    <row r="2431">
+      <c r="A2431" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B2431" t="n">
+        <v>179.88</v>
+      </c>
+      <c r="C2431" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="D2431" t="n">
+        <v>179.74</v>
+      </c>
+      <c r="E2431" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="F2431" t="n">
+        <v>72415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -49032,19 +49032,19 @@
         <v>46232</v>
       </c>
       <c r="B2431" t="n">
-        <v>179.88</v>
+        <v>179.4</v>
       </c>
       <c r="C2431" t="n">
         <v>182.1</v>
       </c>
       <c r="D2431" t="n">
-        <v>179.74</v>
+        <v>179.4</v>
       </c>
       <c r="E2431" t="n">
         <v>182.1</v>
       </c>
       <c r="F2431" t="n">
-        <v>72415</v>
+        <v>172091</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2431"/>
+  <dimension ref="A1:F2432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49032,19 +49032,39 @@
         <v>46232</v>
       </c>
       <c r="B2431" t="n">
-        <v>179.4</v>
+        <v>179.3999938964844</v>
       </c>
       <c r="C2431" t="n">
-        <v>182.1</v>
+        <v>182.1000061035156</v>
       </c>
       <c r="D2431" t="n">
-        <v>179.4</v>
+        <v>179.3999938964844</v>
       </c>
       <c r="E2431" t="n">
-        <v>182.1</v>
+        <v>182.1000061035156</v>
       </c>
       <c r="F2431" t="n">
         <v>172091</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B2432" t="n">
+        <v>183.06</v>
+      </c>
+      <c r="C2432" t="n">
+        <v>183.06</v>
+      </c>
+      <c r="D2432" t="n">
+        <v>179.64</v>
+      </c>
+      <c r="E2432" t="n">
+        <v>180.76</v>
+      </c>
+      <c r="F2432" t="n">
+        <v>261608</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2432"/>
+  <dimension ref="A1:F2433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49052,19 +49052,39 @@
         <v>46233</v>
       </c>
       <c r="B2432" t="n">
-        <v>183.06</v>
+        <v>183.0599975585938</v>
       </c>
       <c r="C2432" t="n">
-        <v>183.06</v>
+        <v>183.0599975585938</v>
       </c>
       <c r="D2432" t="n">
-        <v>179.64</v>
+        <v>179.6399993896484</v>
       </c>
       <c r="E2432" t="n">
-        <v>180.76</v>
+        <v>180.7599945068359</v>
       </c>
       <c r="F2432" t="n">
         <v>261608</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B2433" t="n">
+        <v>183.74</v>
+      </c>
+      <c r="C2433" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="D2433" t="n">
+        <v>183.35</v>
+      </c>
+      <c r="E2433" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="F2433" t="n">
+        <v>289252</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2433"/>
+  <dimension ref="A1:F2434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49072,19 +49072,39 @@
         <v>46234</v>
       </c>
       <c r="B2433" t="n">
-        <v>183.74</v>
+        <v>183.7400054931641</v>
       </c>
       <c r="C2433" t="n">
         <v>184.5</v>
       </c>
       <c r="D2433" t="n">
-        <v>183.35</v>
+        <v>183.3500061035156</v>
       </c>
       <c r="E2433" t="n">
         <v>183.5</v>
       </c>
       <c r="F2433" t="n">
         <v>289252</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B2434" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="C2434" t="n">
+        <v>184.73</v>
+      </c>
+      <c r="D2434" t="n">
+        <v>182.46</v>
+      </c>
+      <c r="E2434" t="n">
+        <v>184.73</v>
+      </c>
+      <c r="F2434" t="n">
+        <v>222293</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2434"/>
+  <dimension ref="A1:F2435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49092,19 +49092,39 @@
         <v>46237</v>
       </c>
       <c r="B2434" t="n">
-        <v>183.45</v>
+        <v>183.4499969482422</v>
       </c>
       <c r="C2434" t="n">
-        <v>184.73</v>
+        <v>184.7299957275391</v>
       </c>
       <c r="D2434" t="n">
-        <v>182.46</v>
+        <v>182.4600067138672</v>
       </c>
       <c r="E2434" t="n">
-        <v>184.73</v>
+        <v>184.7299957275391</v>
       </c>
       <c r="F2434" t="n">
         <v>222293</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B2435" t="n">
+        <v>183.51</v>
+      </c>
+      <c r="C2435" t="n">
+        <v>186.23</v>
+      </c>
+      <c r="D2435" t="n">
+        <v>183.05</v>
+      </c>
+      <c r="E2435" t="n">
+        <v>185.15</v>
+      </c>
+      <c r="F2435" t="n">
+        <v>212714</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2435"/>
+  <dimension ref="A1:F2436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49112,19 +49112,39 @@
         <v>46238</v>
       </c>
       <c r="B2435" t="n">
-        <v>183.51</v>
+        <v>183.5099945068359</v>
       </c>
       <c r="C2435" t="n">
-        <v>186.23</v>
+        <v>186.2700042724609</v>
       </c>
       <c r="D2435" t="n">
-        <v>183.05</v>
+        <v>183.0500030517578</v>
       </c>
       <c r="E2435" t="n">
-        <v>185.15</v>
+        <v>185.1499938964844</v>
       </c>
       <c r="F2435" t="n">
         <v>212714</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B2436" t="n">
+        <v>183.13</v>
+      </c>
+      <c r="C2436" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="D2436" t="n">
+        <v>182.91</v>
+      </c>
+      <c r="E2436" t="n">
+        <v>185.14</v>
+      </c>
+      <c r="F2436" t="n">
+        <v>482916</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2436"/>
+  <dimension ref="A1:F2437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49132,19 +49132,39 @@
         <v>46239</v>
       </c>
       <c r="B2436" t="n">
-        <v>183.13</v>
+        <v>183.1300048828125</v>
       </c>
       <c r="C2436" t="n">
-        <v>185.92</v>
+        <v>185.9199981689453</v>
       </c>
       <c r="D2436" t="n">
-        <v>182.91</v>
+        <v>182.9100036621094</v>
       </c>
       <c r="E2436" t="n">
-        <v>185.14</v>
+        <v>185.1399993896484</v>
       </c>
       <c r="F2436" t="n">
         <v>482916</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B2437" t="n">
+        <v>181.26</v>
+      </c>
+      <c r="C2437" t="n">
+        <v>183.03</v>
+      </c>
+      <c r="D2437" t="n">
+        <v>181.02</v>
+      </c>
+      <c r="E2437" t="n">
+        <v>182.61</v>
+      </c>
+      <c r="F2437" t="n">
+        <v>202192</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2437"/>
+  <dimension ref="A1:F2438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49152,19 +49152,39 @@
         <v>46240</v>
       </c>
       <c r="B2437" t="n">
-        <v>181.26</v>
+        <v>181.2599945068359</v>
       </c>
       <c r="C2437" t="n">
-        <v>183.03</v>
+        <v>183.0299987792969</v>
       </c>
       <c r="D2437" t="n">
-        <v>181.02</v>
+        <v>181.0200042724609</v>
       </c>
       <c r="E2437" t="n">
-        <v>182.61</v>
+        <v>182.6100006103516</v>
       </c>
       <c r="F2437" t="n">
         <v>202192</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B2438" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="C2438" t="n">
+        <v>181.71</v>
+      </c>
+      <c r="D2438" t="n">
+        <v>177.54</v>
+      </c>
+      <c r="E2438" t="n">
+        <v>181.71</v>
+      </c>
+      <c r="F2438" t="n">
+        <v>466796</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2438"/>
+  <dimension ref="A1:F2439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49172,19 +49172,39 @@
         <v>46241</v>
       </c>
       <c r="B2438" t="n">
-        <v>177.8</v>
+        <v>177.8000030517578</v>
       </c>
       <c r="C2438" t="n">
-        <v>181.71</v>
+        <v>181.7100067138672</v>
       </c>
       <c r="D2438" t="n">
-        <v>177.54</v>
+        <v>177.5399932861328</v>
       </c>
       <c r="E2438" t="n">
-        <v>181.71</v>
+        <v>181.7100067138672</v>
       </c>
       <c r="F2438" t="n">
         <v>466796</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B2439" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="C2439" t="n">
+        <v>178.34</v>
+      </c>
+      <c r="D2439" t="n">
+        <v>176.98</v>
+      </c>
+      <c r="E2439" t="n">
+        <v>178.31</v>
+      </c>
+      <c r="F2439" t="n">
+        <v>1014099</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2439"/>
+  <dimension ref="A1:F2440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49195,16 +49195,36 @@
         <v>177.5</v>
       </c>
       <c r="C2439" t="n">
-        <v>178.34</v>
+        <v>178.3399963378906</v>
       </c>
       <c r="D2439" t="n">
-        <v>176.98</v>
+        <v>176.9799957275391</v>
       </c>
       <c r="E2439" t="n">
-        <v>178.31</v>
+        <v>178.3099975585938</v>
       </c>
       <c r="F2439" t="n">
         <v>1014099</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B2440" t="n">
+        <v>173.35</v>
+      </c>
+      <c r="C2440" t="n">
+        <v>178</v>
+      </c>
+      <c r="D2440" t="n">
+        <v>172.84</v>
+      </c>
+      <c r="E2440" t="n">
+        <v>178</v>
+      </c>
+      <c r="F2440" t="n">
+        <v>498563</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2440"/>
+  <dimension ref="A1:F2441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49212,19 +49212,39 @@
         <v>46245</v>
       </c>
       <c r="B2440" t="n">
-        <v>173.35</v>
+        <v>173.3500061035156</v>
       </c>
       <c r="C2440" t="n">
         <v>178</v>
       </c>
       <c r="D2440" t="n">
-        <v>172.84</v>
+        <v>172.8399963378906</v>
       </c>
       <c r="E2440" t="n">
         <v>178</v>
       </c>
       <c r="F2440" t="n">
         <v>498563</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B2441" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="C2441" t="n">
+        <v>173.78</v>
+      </c>
+      <c r="D2441" t="n">
+        <v>172.52</v>
+      </c>
+      <c r="E2441" t="n">
+        <v>173.78</v>
+      </c>
+      <c r="F2441" t="n">
+        <v>638737</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2441"/>
+  <dimension ref="A1:F2442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49232,19 +49232,39 @@
         <v>46246</v>
       </c>
       <c r="B2441" t="n">
-        <v>172.6</v>
+        <v>172.6000061035156</v>
       </c>
       <c r="C2441" t="n">
-        <v>173.78</v>
+        <v>173.7799987792969</v>
       </c>
       <c r="D2441" t="n">
-        <v>172.52</v>
+        <v>172.5200042724609</v>
       </c>
       <c r="E2441" t="n">
-        <v>173.78</v>
+        <v>173.7799987792969</v>
       </c>
       <c r="F2441" t="n">
         <v>638737</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B2442" t="n">
+        <v>172.58</v>
+      </c>
+      <c r="C2442" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="D2442" t="n">
+        <v>171.69</v>
+      </c>
+      <c r="E2442" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="F2442" t="n">
+        <v>356267</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2442"/>
+  <dimension ref="A1:F2443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49251,20 +49251,32 @@
       <c r="A2442" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B2442" t="n">
-        <v>172.58</v>
-      </c>
-      <c r="C2442" t="n">
-        <v>173.82</v>
-      </c>
-      <c r="D2442" t="n">
-        <v>171.69</v>
-      </c>
-      <c r="E2442" t="n">
-        <v>172.6</v>
-      </c>
+      <c r="B2442" t="inlineStr"/>
+      <c r="C2442" t="inlineStr"/>
+      <c r="D2442" t="inlineStr"/>
+      <c r="E2442" t="inlineStr"/>
       <c r="F2442" t="n">
-        <v>356267</v>
+        <v>593280</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B2443" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="C2443" t="n">
+        <v>172.51</v>
+      </c>
+      <c r="D2443" t="n">
+        <v>170.12</v>
+      </c>
+      <c r="E2443" t="n">
+        <v>172</v>
+      </c>
+      <c r="F2443" t="n">
+        <v>593280</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2443"/>
+  <dimension ref="A1:F2444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49251,12 +49251,20 @@
       <c r="A2442" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B2442" t="inlineStr"/>
-      <c r="C2442" t="inlineStr"/>
-      <c r="D2442" t="inlineStr"/>
-      <c r="E2442" t="inlineStr"/>
+      <c r="B2442" t="n">
+        <v>172.5800018310547</v>
+      </c>
+      <c r="C2442" t="n">
+        <v>173.8200073242188</v>
+      </c>
+      <c r="D2442" t="n">
+        <v>171.6900024414062</v>
+      </c>
+      <c r="E2442" t="n">
+        <v>172.6000061035156</v>
+      </c>
       <c r="F2442" t="n">
-        <v>593280</v>
+        <v>356267</v>
       </c>
     </row>
     <row r="2443">
@@ -49264,19 +49272,39 @@
         <v>46248</v>
       </c>
       <c r="B2443" t="n">
-        <v>172.1</v>
+        <v>172.1000061035156</v>
       </c>
       <c r="C2443" t="n">
-        <v>172.51</v>
+        <v>172.5099945068359</v>
       </c>
       <c r="D2443" t="n">
-        <v>170.12</v>
+        <v>170.1199951171875</v>
       </c>
       <c r="E2443" t="n">
         <v>172</v>
       </c>
       <c r="F2443" t="n">
-        <v>593280</v>
+        <v>593281</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B2444" t="n">
+        <v>171.93</v>
+      </c>
+      <c r="C2444" t="n">
+        <v>173.26</v>
+      </c>
+      <c r="D2444" t="n">
+        <v>171.61</v>
+      </c>
+      <c r="E2444" t="n">
+        <v>172.73</v>
+      </c>
+      <c r="F2444" t="n">
+        <v>293550</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2444"/>
+  <dimension ref="A1:F2445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49292,19 +49292,39 @@
         <v>46251</v>
       </c>
       <c r="B2444" t="n">
-        <v>171.93</v>
+        <v>171.9299926757812</v>
       </c>
       <c r="C2444" t="n">
-        <v>173.26</v>
+        <v>173.2599945068359</v>
       </c>
       <c r="D2444" t="n">
-        <v>171.61</v>
+        <v>171.6100006103516</v>
       </c>
       <c r="E2444" t="n">
-        <v>172.73</v>
+        <v>172.7299957275391</v>
       </c>
       <c r="F2444" t="n">
         <v>293550</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B2445" t="n">
+        <v>171.7</v>
+      </c>
+      <c r="C2445" t="n">
+        <v>173.81</v>
+      </c>
+      <c r="D2445" t="n">
+        <v>171.45</v>
+      </c>
+      <c r="E2445" t="n">
+        <v>172.28</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>441886</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2445"/>
+  <dimension ref="A1:F2446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49312,19 +49312,39 @@
         <v>46252</v>
       </c>
       <c r="B2445" t="n">
-        <v>171.7</v>
+        <v>171.6999969482422</v>
       </c>
       <c r="C2445" t="n">
-        <v>173.81</v>
+        <v>173.8099975585938</v>
       </c>
       <c r="D2445" t="n">
-        <v>171.45</v>
+        <v>171.4499969482422</v>
       </c>
       <c r="E2445" t="n">
-        <v>172.28</v>
+        <v>172.2799987792969</v>
       </c>
       <c r="F2445" t="n">
         <v>441886</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2446" t="n">
+        <v>173.38</v>
+      </c>
+      <c r="C2446" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="D2446" t="n">
+        <v>172.96</v>
+      </c>
+      <c r="E2446" t="n">
+        <v>173.45</v>
+      </c>
+      <c r="F2446" t="n">
+        <v>334626</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2446"/>
+  <dimension ref="A1:F2447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49332,19 +49332,39 @@
         <v>46253</v>
       </c>
       <c r="B2446" t="n">
-        <v>173.38</v>
+        <v>173.3800048828125</v>
       </c>
       <c r="C2446" t="n">
-        <v>175.9</v>
+        <v>175.8999938964844</v>
       </c>
       <c r="D2446" t="n">
-        <v>172.96</v>
+        <v>172.9600067138672</v>
       </c>
       <c r="E2446" t="n">
-        <v>173.45</v>
+        <v>173.4499969482422</v>
       </c>
       <c r="F2446" t="n">
         <v>334626</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B2447" t="n">
+        <v>173.36</v>
+      </c>
+      <c r="C2447" t="n">
+        <v>174.99</v>
+      </c>
+      <c r="D2447" t="n">
+        <v>172.32</v>
+      </c>
+      <c r="E2447" t="n">
+        <v>172.78</v>
+      </c>
+      <c r="F2447" t="n">
+        <v>1278293</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2447"/>
+  <dimension ref="A1:F2448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49352,19 +49352,39 @@
         <v>46254</v>
       </c>
       <c r="B2447" t="n">
-        <v>173.36</v>
+        <v>173.3600006103516</v>
       </c>
       <c r="C2447" t="n">
-        <v>174.99</v>
+        <v>174.9499969482422</v>
       </c>
       <c r="D2447" t="n">
-        <v>172.32</v>
+        <v>172.3200073242188</v>
       </c>
       <c r="E2447" t="n">
-        <v>172.78</v>
+        <v>172.7799987792969</v>
       </c>
       <c r="F2447" t="n">
         <v>1278293</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B2448" t="n">
+        <v>176.42</v>
+      </c>
+      <c r="C2448" t="n">
+        <v>177.56</v>
+      </c>
+      <c r="D2448" t="n">
+        <v>173.93</v>
+      </c>
+      <c r="E2448" t="n">
+        <v>174.3</v>
+      </c>
+      <c r="F2448" t="n">
+        <v>368531</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2448"/>
+  <dimension ref="A1:F2449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49372,19 +49372,39 @@
         <v>46255</v>
       </c>
       <c r="B2448" t="n">
-        <v>176.42</v>
+        <v>176.4199981689453</v>
       </c>
       <c r="C2448" t="n">
-        <v>177.56</v>
+        <v>177.5200042724609</v>
       </c>
       <c r="D2448" t="n">
-        <v>173.93</v>
+        <v>173.9299926757812</v>
       </c>
       <c r="E2448" t="n">
-        <v>174.3</v>
+        <v>174.3000030517578</v>
       </c>
       <c r="F2448" t="n">
         <v>368531</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B2449" t="n">
+        <v>177.42</v>
+      </c>
+      <c r="C2449" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="D2449" t="n">
+        <v>174.79</v>
+      </c>
+      <c r="E2449" t="n">
+        <v>175.79</v>
+      </c>
+      <c r="F2449" t="n">
+        <v>662678</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2449"/>
+  <dimension ref="A1:F2450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49391,20 +49391,32 @@
       <c r="A2449" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B2449" t="n">
-        <v>177.42</v>
-      </c>
-      <c r="C2449" t="n">
-        <v>178.7</v>
-      </c>
-      <c r="D2449" t="n">
-        <v>174.79</v>
-      </c>
-      <c r="E2449" t="n">
-        <v>175.79</v>
-      </c>
+      <c r="B2449" t="inlineStr"/>
+      <c r="C2449" t="inlineStr"/>
+      <c r="D2449" t="inlineStr"/>
+      <c r="E2449" t="inlineStr"/>
       <c r="F2449" t="n">
-        <v>662678</v>
+        <v>919212</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B2450" t="n">
+        <v>180.46</v>
+      </c>
+      <c r="C2450" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="D2450" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="E2450" t="n">
+        <v>177.88</v>
+      </c>
+      <c r="F2450" t="n">
+        <v>919673</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2450"/>
+  <dimension ref="A1:F2451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49391,12 +49391,20 @@
       <c r="A2449" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B2449" t="inlineStr"/>
-      <c r="C2449" t="inlineStr"/>
-      <c r="D2449" t="inlineStr"/>
-      <c r="E2449" t="inlineStr"/>
+      <c r="B2449" t="n">
+        <v>177.4199981689453</v>
+      </c>
+      <c r="C2449" t="n">
+        <v>178.6999969482422</v>
+      </c>
+      <c r="D2449" t="n">
+        <v>174.7899932861328</v>
+      </c>
+      <c r="E2449" t="n">
+        <v>175.7899932861328</v>
+      </c>
       <c r="F2449" t="n">
-        <v>919212</v>
+        <v>662678</v>
       </c>
     </row>
     <row r="2450">
@@ -49404,7 +49412,7 @@
         <v>46259</v>
       </c>
       <c r="B2450" t="n">
-        <v>180.46</v>
+        <v>180.4600067138672</v>
       </c>
       <c r="C2450" t="n">
         <v>180.5</v>
@@ -49413,10 +49421,30 @@
         <v>176.75</v>
       </c>
       <c r="E2450" t="n">
-        <v>177.88</v>
+        <v>177.8800048828125</v>
       </c>
       <c r="F2450" t="n">
         <v>919673</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B2451" t="n">
+        <v>180.2100067138672</v>
+      </c>
+      <c r="C2451" t="n">
+        <v>182.0599975585938</v>
+      </c>
+      <c r="D2451" t="n">
+        <v>179.8699951171875</v>
+      </c>
+      <c r="E2451" t="n">
+        <v>180.6999969482422</v>
+      </c>
+      <c r="F2451" t="n">
+        <v>757356</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2451"/>
+  <dimension ref="A1:F2452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49444,7 +49444,27 @@
         <v>180.6999969482422</v>
       </c>
       <c r="F2451" t="n">
-        <v>757356</v>
+        <v>857858</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B2452" t="n">
+        <v>180.67</v>
+      </c>
+      <c r="C2452" t="n">
+        <v>181.18</v>
+      </c>
+      <c r="D2452" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="E2452" t="n">
+        <v>179.71</v>
+      </c>
+      <c r="F2452" t="n">
+        <v>1889137</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2452"/>
+  <dimension ref="A1:F2453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49451,20 +49451,32 @@
       <c r="A2452" s="1" t="n">
         <v>46261</v>
       </c>
-      <c r="B2452" t="n">
-        <v>180.67</v>
-      </c>
-      <c r="C2452" t="n">
-        <v>181.18</v>
-      </c>
-      <c r="D2452" t="n">
-        <v>179.25</v>
-      </c>
-      <c r="E2452" t="n">
-        <v>179.71</v>
-      </c>
+      <c r="B2452" t="inlineStr"/>
+      <c r="C2452" t="inlineStr"/>
+      <c r="D2452" t="inlineStr"/>
+      <c r="E2452" t="inlineStr"/>
       <c r="F2452" t="n">
-        <v>1889137</v>
+        <v>231275</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B2453" t="n">
+        <v>180.26</v>
+      </c>
+      <c r="C2453" t="n">
+        <v>182.09</v>
+      </c>
+      <c r="D2453" t="n">
+        <v>179.42</v>
+      </c>
+      <c r="E2453" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="F2453" t="n">
+        <v>231262</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -49456,7 +49456,7 @@
       <c r="D2452" t="inlineStr"/>
       <c r="E2452" t="inlineStr"/>
       <c r="F2452" t="n">
-        <v>231275</v>
+        <v>442725</v>
       </c>
     </row>
     <row r="2453">
@@ -49464,7 +49464,7 @@
         <v>46262</v>
       </c>
       <c r="B2453" t="n">
-        <v>180.26</v>
+        <v>181.24</v>
       </c>
       <c r="C2453" t="n">
         <v>182.09</v>
@@ -49476,7 +49476,7 @@
         <v>181.75</v>
       </c>
       <c r="F2453" t="n">
-        <v>231262</v>
+        <v>442725</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2453"/>
+  <dimension ref="A1:F2452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49449,7 +49449,7 @@
     </row>
     <row r="2452">
       <c r="A2452" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B2452" t="inlineStr"/>
       <c r="C2452" t="inlineStr"/>
@@ -49459,26 +49459,6 @@
         <v>442725</v>
       </c>
     </row>
-    <row r="2453">
-      <c r="A2453" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B2453" t="n">
-        <v>181.24</v>
-      </c>
-      <c r="C2453" t="n">
-        <v>182.09</v>
-      </c>
-      <c r="D2453" t="n">
-        <v>179.42</v>
-      </c>
-      <c r="E2453" t="n">
-        <v>181.75</v>
-      </c>
-      <c r="F2453" t="n">
-        <v>442725</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2452"/>
+  <dimension ref="A1:F2455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49449,14 +49449,82 @@
     </row>
     <row r="2452">
       <c r="A2452" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B2452" t="n">
+        <v>180.6699981689453</v>
+      </c>
+      <c r="C2452" t="n">
+        <v>181.1799926757812</v>
+      </c>
+      <c r="D2452" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="E2452" t="n">
+        <v>179.7100067138672</v>
+      </c>
+      <c r="F2452" t="n">
+        <v>1889137</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B2452" t="inlineStr"/>
-      <c r="C2452" t="inlineStr"/>
-      <c r="D2452" t="inlineStr"/>
-      <c r="E2452" t="inlineStr"/>
-      <c r="F2452" t="n">
+      <c r="B2453" t="n">
+        <v>181.2400054931641</v>
+      </c>
+      <c r="C2453" t="n">
+        <v>182.0899963378906</v>
+      </c>
+      <c r="D2453" t="n">
+        <v>179.4199981689453</v>
+      </c>
+      <c r="E2453" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="F2453" t="n">
         <v>442725</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B2454" t="n">
+        <v>183.3200073242188</v>
+      </c>
+      <c r="C2454" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="D2454" t="n">
+        <v>182.7400054931641</v>
+      </c>
+      <c r="E2454" t="n">
+        <v>183.5099945068359</v>
+      </c>
+      <c r="F2454" t="n">
+        <v>172391</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B2455" t="n">
+        <v>185.61</v>
+      </c>
+      <c r="C2455" t="n">
+        <v>186.92</v>
+      </c>
+      <c r="D2455" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="E2455" t="n">
+        <v>184.66</v>
+      </c>
+      <c r="F2455" t="n">
+        <v>229525</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2455"/>
+  <dimension ref="A1:F2456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49511,20 +49511,32 @@
       <c r="A2455" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B2455" t="n">
-        <v>185.61</v>
-      </c>
-      <c r="C2455" t="n">
-        <v>186.92</v>
-      </c>
-      <c r="D2455" t="n">
-        <v>183.22</v>
-      </c>
-      <c r="E2455" t="n">
-        <v>184.66</v>
-      </c>
+      <c r="B2455" t="inlineStr"/>
+      <c r="C2455" t="inlineStr"/>
+      <c r="D2455" t="inlineStr"/>
+      <c r="E2455" t="inlineStr"/>
       <c r="F2455" t="n">
-        <v>229525</v>
+        <v>749912</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B2456" t="n">
+        <v>191.35</v>
+      </c>
+      <c r="C2456" t="n">
+        <v>192.28</v>
+      </c>
+      <c r="D2456" t="n">
+        <v>186.14</v>
+      </c>
+      <c r="E2456" t="n">
+        <v>187.16</v>
+      </c>
+      <c r="F2456" t="n">
+        <v>749915</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2456"/>
+  <dimension ref="A1:F2457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49511,12 +49511,20 @@
       <c r="A2455" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B2455" t="inlineStr"/>
-      <c r="C2455" t="inlineStr"/>
-      <c r="D2455" t="inlineStr"/>
-      <c r="E2455" t="inlineStr"/>
+      <c r="B2455" t="n">
+        <v>185.6100006103516</v>
+      </c>
+      <c r="C2455" t="n">
+        <v>186.9199981689453</v>
+      </c>
+      <c r="D2455" t="n">
+        <v>183.2200012207031</v>
+      </c>
+      <c r="E2455" t="n">
+        <v>184.6600036621094</v>
+      </c>
       <c r="F2455" t="n">
-        <v>749912</v>
+        <v>229525</v>
       </c>
     </row>
     <row r="2456">
@@ -49524,19 +49532,39 @@
         <v>46267</v>
       </c>
       <c r="B2456" t="n">
-        <v>191.35</v>
+        <v>191.3500061035156</v>
       </c>
       <c r="C2456" t="n">
-        <v>192.28</v>
+        <v>192.1499938964844</v>
       </c>
       <c r="D2456" t="n">
-        <v>186.14</v>
+        <v>186.1399993896484</v>
       </c>
       <c r="E2456" t="n">
-        <v>187.16</v>
+        <v>187.1600036621094</v>
       </c>
       <c r="F2456" t="n">
         <v>749915</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B2457" t="n">
+        <v>191.28</v>
+      </c>
+      <c r="C2457" t="n">
+        <v>195</v>
+      </c>
+      <c r="D2457" t="n">
+        <v>190.63</v>
+      </c>
+      <c r="E2457" t="n">
+        <v>193.59</v>
+      </c>
+      <c r="F2457" t="n">
+        <v>1555076</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2457"/>
+  <dimension ref="A1:F2458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49551,20 +49551,32 @@
       <c r="A2457" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B2457" t="n">
-        <v>191.28</v>
-      </c>
-      <c r="C2457" t="n">
-        <v>195</v>
-      </c>
-      <c r="D2457" t="n">
-        <v>190.63</v>
-      </c>
-      <c r="E2457" t="n">
-        <v>193.59</v>
-      </c>
+      <c r="B2457" t="inlineStr"/>
+      <c r="C2457" t="inlineStr"/>
+      <c r="D2457" t="inlineStr"/>
+      <c r="E2457" t="inlineStr"/>
       <c r="F2457" t="n">
-        <v>1555076</v>
+        <v>427100</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B2458" t="n">
+        <v>191</v>
+      </c>
+      <c r="C2458" t="n">
+        <v>192.54</v>
+      </c>
+      <c r="D2458" t="n">
+        <v>189.09</v>
+      </c>
+      <c r="E2458" t="n">
+        <v>190.43</v>
+      </c>
+      <c r="F2458" t="n">
+        <v>427120</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -49551,12 +49551,20 @@
       <c r="A2457" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B2457" t="inlineStr"/>
-      <c r="C2457" t="inlineStr"/>
-      <c r="D2457" t="inlineStr"/>
-      <c r="E2457" t="inlineStr"/>
+      <c r="B2457" t="n">
+        <v>191.2799987792969</v>
+      </c>
+      <c r="C2457" t="n">
+        <v>195</v>
+      </c>
+      <c r="D2457" t="n">
+        <v>190.6300048828125</v>
+      </c>
+      <c r="E2457" t="n">
+        <v>193.5899963378906</v>
+      </c>
       <c r="F2457" t="n">
-        <v>427100</v>
+        <v>1555076</v>
       </c>
     </row>
     <row r="2458">
@@ -49567,13 +49575,13 @@
         <v>191</v>
       </c>
       <c r="C2458" t="n">
-        <v>192.54</v>
+        <v>192.5399932861328</v>
       </c>
       <c r="D2458" t="n">
-        <v>189.09</v>
+        <v>189.0899963378906</v>
       </c>
       <c r="E2458" t="n">
-        <v>190.43</v>
+        <v>190.4299926757812</v>
       </c>
       <c r="F2458" t="n">
         <v>427120</v>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2458"/>
+  <dimension ref="A1:F2459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49587,6 +49587,26 @@
         <v>427120</v>
       </c>
     </row>
+    <row r="2459">
+      <c r="A2459" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B2459" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="C2459" t="n">
+        <v>195.77</v>
+      </c>
+      <c r="D2459" t="n">
+        <v>193.12</v>
+      </c>
+      <c r="E2459" t="n">
+        <v>193.12</v>
+      </c>
+      <c r="F2459" t="n">
+        <v>334356</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2459"/>
+  <dimension ref="A1:F2460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49607,6 +49607,26 @@
         <v>334356</v>
       </c>
     </row>
+    <row r="2460">
+      <c r="A2460" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B2460" t="n">
+        <v>191.62</v>
+      </c>
+      <c r="C2460" t="n">
+        <v>193.11</v>
+      </c>
+      <c r="D2460" t="n">
+        <v>190.67</v>
+      </c>
+      <c r="E2460" t="n">
+        <v>192.81</v>
+      </c>
+      <c r="F2460" t="n">
+        <v>268986</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2460"/>
+  <dimension ref="A1:F2461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49595,13 +49595,13 @@
         <v>193.5</v>
       </c>
       <c r="C2459" t="n">
-        <v>195.77</v>
+        <v>195.7700042724609</v>
       </c>
       <c r="D2459" t="n">
-        <v>193.12</v>
+        <v>193.1199951171875</v>
       </c>
       <c r="E2459" t="n">
-        <v>193.12</v>
+        <v>193.1199951171875</v>
       </c>
       <c r="F2459" t="n">
         <v>334356</v>
@@ -49612,19 +49612,39 @@
         <v>46274</v>
       </c>
       <c r="B2460" t="n">
-        <v>191.62</v>
+        <v>191.6199951171875</v>
       </c>
       <c r="C2460" t="n">
-        <v>193.11</v>
+        <v>193.0200042724609</v>
       </c>
       <c r="D2460" t="n">
-        <v>190.67</v>
+        <v>190.6799926757812</v>
       </c>
       <c r="E2460" t="n">
-        <v>192.81</v>
+        <v>192.8099975585938</v>
       </c>
       <c r="F2460" t="n">
         <v>268986</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B2461" t="n">
+        <v>194.26</v>
+      </c>
+      <c r="C2461" t="n">
+        <v>194.76</v>
+      </c>
+      <c r="D2461" t="n">
+        <v>190.46</v>
+      </c>
+      <c r="E2461" t="n">
+        <v>191.18</v>
+      </c>
+      <c r="F2461" t="n">
+        <v>310658</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2461"/>
+  <dimension ref="A1:F2462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49632,19 +49632,39 @@
         <v>46275</v>
       </c>
       <c r="B2461" t="n">
-        <v>194.26</v>
+        <v>194.2599945068359</v>
       </c>
       <c r="C2461" t="n">
-        <v>194.76</v>
+        <v>194.7599945068359</v>
       </c>
       <c r="D2461" t="n">
-        <v>190.46</v>
+        <v>190.4600067138672</v>
       </c>
       <c r="E2461" t="n">
-        <v>191.18</v>
+        <v>191.1799926757812</v>
       </c>
       <c r="F2461" t="n">
         <v>310658</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B2462" t="n">
+        <v>193.1</v>
+      </c>
+      <c r="C2462" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="D2462" t="n">
+        <v>192.18</v>
+      </c>
+      <c r="E2462" t="n">
+        <v>194.26</v>
+      </c>
+      <c r="F2462" t="n">
+        <v>829811</v>
       </c>
     </row>
   </sheetData>
